--- a/jp_test_spec_generator/output/test_spec.xlsx
+++ b/jp_test_spec_generator/output/test_spec.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -99,7 +109,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -470,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -776,1559 +792,1688 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PCL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>E,L</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>E,L</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>E,L</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>E,L</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>E,L</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>チェック条件</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>C-001</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>通常モードで画面を起動する</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr"/>
-      <c r="X6" s="7" t="inlineStr"/>
-      <c r="Y6" s="7" t="inlineStr"/>
-      <c r="Z6" s="7" t="inlineStr"/>
-      <c r="AA6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>C-002</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>一覧表示対象データが存在する状態で画面を起動する</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr"/>
-      <c r="T7" s="7" t="inlineStr"/>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="inlineStr"/>
-      <c r="W7" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X7" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Y7" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Z7" s="7" t="inlineStr"/>
-      <c r="AA7" s="7" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V7" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W7" s="9" t="inlineStr"/>
+      <c r="X7" s="9" t="inlineStr"/>
+      <c r="Y7" s="9" t="inlineStr"/>
+      <c r="Z7" s="9" t="inlineStr"/>
+      <c r="AA7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>C-003</t>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>C-002</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>参照モードで画面を起動する</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr"/>
-      <c r="P8" s="7" t="inlineStr"/>
-      <c r="Q8" s="7" t="inlineStr"/>
-      <c r="R8" s="7" t="inlineStr"/>
-      <c r="S8" s="7" t="inlineStr"/>
-      <c r="T8" s="7" t="inlineStr"/>
-      <c r="U8" s="7" t="inlineStr"/>
-      <c r="V8" s="7" t="inlineStr"/>
-      <c r="W8" s="7" t="inlineStr"/>
-      <c r="X8" s="7" t="inlineStr"/>
-      <c r="Y8" s="7" t="inlineStr"/>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA8" s="7" t="inlineStr"/>
+          <t>一覧表示対象データが存在する状態で画面を起動する</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr"/>
+      <c r="O8" s="9" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr"/>
+      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="R8" s="9" t="inlineStr"/>
+      <c r="S8" s="9" t="inlineStr"/>
+      <c r="T8" s="9" t="inlineStr"/>
+      <c r="U8" s="9" t="inlineStr"/>
+      <c r="V8" s="9" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z8" s="9" t="inlineStr"/>
+      <c r="AA8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>C-004</t>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>対象データが更新済みの状態で更新処理を実行する</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="7" t="inlineStr"/>
-      <c r="T9" s="7" t="inlineStr"/>
-      <c r="U9" s="7" t="inlineStr"/>
-      <c r="V9" s="7" t="inlineStr"/>
-      <c r="W9" s="7" t="inlineStr"/>
-      <c r="X9" s="7" t="inlineStr"/>
-      <c r="Y9" s="7" t="inlineStr"/>
-      <c r="Z9" s="7" t="inlineStr"/>
-      <c r="AA9" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>参照モードで画面を起動する</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr"/>
+      <c r="O9" s="9" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
+      <c r="Q9" s="9" t="inlineStr"/>
+      <c r="R9" s="9" t="inlineStr"/>
+      <c r="S9" s="9" t="inlineStr"/>
+      <c r="T9" s="9" t="inlineStr"/>
+      <c r="U9" s="9" t="inlineStr"/>
+      <c r="V9" s="9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr"/>
+      <c r="X9" s="9" t="inlineStr"/>
+      <c r="Y9" s="9" t="inlineStr"/>
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="2" t="n"/>
-      <c r="Z10" s="2" t="n"/>
-      <c r="AA10" s="2" t="n"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>C-004</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>対象データが更新済みの状態で更新処理を実行する</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
+      <c r="O10" s="9" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="R10" s="9" t="inlineStr"/>
+      <c r="S10" s="9" t="inlineStr"/>
+      <c r="T10" s="9" t="inlineStr"/>
+      <c r="U10" s="9" t="inlineStr"/>
+      <c r="V10" s="9" t="inlineStr"/>
+      <c r="W10" s="9" t="inlineStr"/>
+      <c r="X10" s="9" t="inlineStr"/>
+      <c r="Y10" s="9" t="inlineStr"/>
+      <c r="Z10" s="9" t="inlineStr"/>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
+      <c r="AA11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>アクション</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>A-001</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>画面を起動する</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="7" t="inlineStr"/>
-      <c r="U11" s="7" t="inlineStr"/>
-      <c r="V11" s="7" t="inlineStr"/>
-      <c r="W11" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X11" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Y11" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Z11" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>A-002</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>対象項目を確認する</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr"/>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr"/>
-      <c r="T12" s="7" t="inlineStr"/>
-      <c r="U12" s="7" t="inlineStr"/>
-      <c r="V12" s="7" t="inlineStr"/>
-      <c r="W12" s="7" t="inlineStr"/>
-      <c r="X12" s="7" t="inlineStr"/>
-      <c r="Y12" s="7" t="inlineStr"/>
-      <c r="Z12" s="7" t="inlineStr"/>
-      <c r="AA12" s="7" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr"/>
+      <c r="O12" s="9" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
+      <c r="Q12" s="9" t="inlineStr"/>
+      <c r="R12" s="9" t="inlineStr"/>
+      <c r="S12" s="9" t="inlineStr"/>
+      <c r="T12" s="9" t="inlineStr"/>
+      <c r="U12" s="9" t="inlineStr"/>
+      <c r="V12" s="9" t="inlineStr"/>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y12" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>A-003</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>A-002</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>対象項目に規定外の値を入力する</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr"/>
-      <c r="T13" s="7" t="inlineStr"/>
-      <c r="U13" s="7" t="inlineStr"/>
-      <c r="V13" s="7" t="inlineStr"/>
-      <c r="W13" s="7" t="inlineStr"/>
-      <c r="X13" s="7" t="inlineStr"/>
-      <c r="Y13" s="7" t="inlineStr"/>
-      <c r="Z13" s="7" t="inlineStr"/>
-      <c r="AA13" s="7" t="inlineStr"/>
+          <t>対象項目を確認する</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr"/>
+      <c r="O13" s="9" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
+      <c r="Q13" s="9" t="inlineStr"/>
+      <c r="R13" s="9" t="inlineStr"/>
+      <c r="S13" s="9" t="inlineStr"/>
+      <c r="T13" s="9" t="inlineStr"/>
+      <c r="U13" s="9" t="inlineStr"/>
+      <c r="V13" s="9" t="inlineStr"/>
+      <c r="W13" s="9" t="inlineStr"/>
+      <c r="X13" s="9" t="inlineStr"/>
+      <c r="Y13" s="9" t="inlineStr"/>
+      <c r="Z13" s="9" t="inlineStr"/>
+      <c r="AA13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>A-004</t>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>A-003</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>対象イベントを実行する</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr"/>
-      <c r="Q14" s="7" t="inlineStr"/>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W14" s="7" t="inlineStr"/>
-      <c r="X14" s="7" t="inlineStr"/>
-      <c r="Y14" s="7" t="inlineStr"/>
-      <c r="Z14" s="7" t="inlineStr"/>
-      <c r="AA14" s="7" t="inlineStr"/>
+          <t>対象項目に規定外の値を入力する</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr"/>
+      <c r="T14" s="9" t="inlineStr"/>
+      <c r="U14" s="9" t="inlineStr"/>
+      <c r="V14" s="9" t="inlineStr"/>
+      <c r="W14" s="9" t="inlineStr"/>
+      <c r="X14" s="9" t="inlineStr"/>
+      <c r="Y14" s="9" t="inlineStr"/>
+      <c r="Z14" s="9" t="inlineStr"/>
+      <c r="AA14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>A-005</t>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>A-004</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>更新処理を実行する</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr"/>
-      <c r="T15" s="7" t="inlineStr"/>
-      <c r="U15" s="7" t="inlineStr"/>
-      <c r="V15" s="7" t="inlineStr"/>
-      <c r="W15" s="7" t="inlineStr"/>
-      <c r="X15" s="7" t="inlineStr"/>
-      <c r="Y15" s="7" t="inlineStr"/>
-      <c r="Z15" s="7" t="inlineStr"/>
-      <c r="AA15" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>対象イベントを実行する</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr"/>
+      <c r="N15" s="9" t="inlineStr"/>
+      <c r="O15" s="9" t="inlineStr"/>
+      <c r="P15" s="9" t="inlineStr"/>
+      <c r="Q15" s="9" t="inlineStr"/>
+      <c r="R15" s="9" t="inlineStr"/>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr"/>
+      <c r="X15" s="9" t="inlineStr"/>
+      <c r="Y15" s="9" t="inlineStr"/>
+      <c r="Z15" s="9" t="inlineStr"/>
+      <c r="AA15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="n"/>
-      <c r="Y16" s="2" t="n"/>
-      <c r="Z16" s="2" t="n"/>
-      <c r="AA16" s="2" t="n"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>A-005</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>更新処理を実行する</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr"/>
+      <c r="O16" s="9" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr"/>
+      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="R16" s="9" t="inlineStr"/>
+      <c r="S16" s="9" t="inlineStr"/>
+      <c r="T16" s="9" t="inlineStr"/>
+      <c r="U16" s="9" t="inlineStr"/>
+      <c r="V16" s="9" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr"/>
+      <c r="X16" s="9" t="inlineStr"/>
+      <c r="Y16" s="9" t="inlineStr"/>
+      <c r="Z16" s="9" t="inlineStr"/>
+      <c r="AA16" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="n"/>
+      <c r="Z17" s="2" t="n"/>
+      <c r="AA17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>確認内容</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>E-001</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>主要入力項目が初期表示されること</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr"/>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr"/>
-      <c r="T17" s="7" t="inlineStr"/>
-      <c r="U17" s="7" t="inlineStr"/>
-      <c r="V17" s="7" t="inlineStr"/>
-      <c r="W17" s="7" t="inlineStr"/>
-      <c r="X17" s="7" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="7" t="inlineStr"/>
-      <c r="AA17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>E-002</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>主要ボタンが初期表示されること</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
-      <c r="J18" s="7" t="inlineStr"/>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr"/>
-      <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr"/>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr"/>
-      <c r="T18" s="7" t="inlineStr"/>
-      <c r="U18" s="7" t="inlineStr"/>
-      <c r="V18" s="7" t="inlineStr"/>
-      <c r="W18" s="7" t="inlineStr"/>
-      <c r="X18" s="7" t="inlineStr"/>
-      <c r="Y18" s="7" t="inlineStr"/>
-      <c r="Z18" s="7" t="inlineStr"/>
-      <c r="AA18" s="7" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr"/>
+      <c r="N18" s="9" t="inlineStr"/>
+      <c r="O18" s="9" t="inlineStr"/>
+      <c r="P18" s="9" t="inlineStr"/>
+      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="R18" s="9" t="inlineStr"/>
+      <c r="S18" s="9" t="inlineStr"/>
+      <c r="T18" s="9" t="inlineStr"/>
+      <c r="U18" s="9" t="inlineStr"/>
+      <c r="V18" s="9" t="inlineStr"/>
+      <c r="W18" s="9" t="inlineStr"/>
+      <c r="X18" s="9" t="inlineStr"/>
+      <c r="Y18" s="9" t="inlineStr"/>
+      <c r="Z18" s="9" t="inlineStr"/>
+      <c r="AA18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>E-003</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>E-002</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>一覧領域が初期状態で表示されること</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr"/>
-      <c r="Q19" s="7" t="inlineStr"/>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr"/>
-      <c r="T19" s="7" t="inlineStr"/>
-      <c r="U19" s="7" t="inlineStr"/>
-      <c r="V19" s="7" t="inlineStr"/>
-      <c r="W19" s="7" t="inlineStr"/>
-      <c r="X19" s="7" t="inlineStr"/>
-      <c r="Y19" s="7" t="inlineStr"/>
-      <c r="Z19" s="7" t="inlineStr"/>
-      <c r="AA19" s="7" t="inlineStr"/>
+          <t>主要ボタンが初期表示されること</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr"/>
+      <c r="N19" s="9" t="inlineStr"/>
+      <c r="O19" s="9" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
+      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="R19" s="9" t="inlineStr"/>
+      <c r="S19" s="9" t="inlineStr"/>
+      <c r="T19" s="9" t="inlineStr"/>
+      <c r="U19" s="9" t="inlineStr"/>
+      <c r="V19" s="9" t="inlineStr"/>
+      <c r="W19" s="9" t="inlineStr"/>
+      <c r="X19" s="9" t="inlineStr"/>
+      <c r="Y19" s="9" t="inlineStr"/>
+      <c r="Z19" s="9" t="inlineStr"/>
+      <c r="AA19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>E-004</t>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>E-003</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>店番・店名 が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr"/>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr"/>
-      <c r="P20" s="7" t="inlineStr"/>
-      <c r="Q20" s="7" t="inlineStr"/>
-      <c r="R20" s="7" t="inlineStr"/>
-      <c r="S20" s="7" t="inlineStr"/>
-      <c r="T20" s="7" t="inlineStr"/>
-      <c r="U20" s="7" t="inlineStr"/>
-      <c r="V20" s="7" t="inlineStr"/>
-      <c r="W20" s="7" t="inlineStr"/>
-      <c r="X20" s="7" t="inlineStr"/>
-      <c r="Y20" s="7" t="inlineStr"/>
-      <c r="Z20" s="7" t="inlineStr"/>
-      <c r="AA20" s="7" t="inlineStr"/>
+          <t>一覧領域が初期状態で表示されること</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr"/>
+      <c r="N20" s="9" t="inlineStr"/>
+      <c r="O20" s="9" t="inlineStr"/>
+      <c r="P20" s="9" t="inlineStr"/>
+      <c r="Q20" s="9" t="inlineStr"/>
+      <c r="R20" s="9" t="inlineStr"/>
+      <c r="S20" s="9" t="inlineStr"/>
+      <c r="T20" s="9" t="inlineStr"/>
+      <c r="U20" s="9" t="inlineStr"/>
+      <c r="V20" s="9" t="inlineStr"/>
+      <c r="W20" s="9" t="inlineStr"/>
+      <c r="X20" s="9" t="inlineStr"/>
+      <c r="Y20" s="9" t="inlineStr"/>
+      <c r="Z20" s="9" t="inlineStr"/>
+      <c r="AA20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>E-005</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>E-004</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>顧客番号 が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="7" t="inlineStr"/>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="7" t="inlineStr"/>
-      <c r="U21" s="7" t="inlineStr"/>
-      <c r="V21" s="7" t="inlineStr"/>
-      <c r="W21" s="7" t="inlineStr"/>
-      <c r="X21" s="7" t="inlineStr"/>
-      <c r="Y21" s="7" t="inlineStr"/>
-      <c r="Z21" s="7" t="inlineStr"/>
-      <c r="AA21" s="7" t="inlineStr"/>
+          <t>店番・店名 が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr"/>
+      <c r="N21" s="9" t="inlineStr"/>
+      <c r="O21" s="9" t="inlineStr"/>
+      <c r="P21" s="9" t="inlineStr"/>
+      <c r="Q21" s="9" t="inlineStr"/>
+      <c r="R21" s="9" t="inlineStr"/>
+      <c r="S21" s="9" t="inlineStr"/>
+      <c r="T21" s="9" t="inlineStr"/>
+      <c r="U21" s="9" t="inlineStr"/>
+      <c r="V21" s="9" t="inlineStr"/>
+      <c r="W21" s="9" t="inlineStr"/>
+      <c r="X21" s="9" t="inlineStr"/>
+      <c r="Y21" s="9" t="inlineStr"/>
+      <c r="Z21" s="9" t="inlineStr"/>
+      <c r="AA21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>E-006</t>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>E-005</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>事象ステータス が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr"/>
-      <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr"/>
-      <c r="P22" s="7" t="inlineStr"/>
-      <c r="Q22" s="7" t="inlineStr"/>
-      <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="7" t="inlineStr"/>
-      <c r="T22" s="7" t="inlineStr"/>
-      <c r="U22" s="7" t="inlineStr"/>
-      <c r="V22" s="7" t="inlineStr"/>
-      <c r="W22" s="7" t="inlineStr"/>
-      <c r="X22" s="7" t="inlineStr"/>
-      <c r="Y22" s="7" t="inlineStr"/>
-      <c r="Z22" s="7" t="inlineStr"/>
-      <c r="AA22" s="7" t="inlineStr"/>
+          <t>顧客番号 が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr"/>
+      <c r="N22" s="9" t="inlineStr"/>
+      <c r="O22" s="9" t="inlineStr"/>
+      <c r="P22" s="9" t="inlineStr"/>
+      <c r="Q22" s="9" t="inlineStr"/>
+      <c r="R22" s="9" t="inlineStr"/>
+      <c r="S22" s="9" t="inlineStr"/>
+      <c r="T22" s="9" t="inlineStr"/>
+      <c r="U22" s="9" t="inlineStr"/>
+      <c r="V22" s="9" t="inlineStr"/>
+      <c r="W22" s="9" t="inlineStr"/>
+      <c r="X22" s="9" t="inlineStr"/>
+      <c r="Y22" s="9" t="inlineStr"/>
+      <c r="Z22" s="9" t="inlineStr"/>
+      <c r="AA22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>E-007</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>E-006</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>事故及び延滞に至った原因 が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr"/>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr"/>
-      <c r="P23" s="7" t="inlineStr"/>
-      <c r="Q23" s="7" t="inlineStr"/>
-      <c r="R23" s="7" t="inlineStr"/>
-      <c r="S23" s="7" t="inlineStr"/>
-      <c r="T23" s="7" t="inlineStr"/>
-      <c r="U23" s="7" t="inlineStr"/>
-      <c r="V23" s="7" t="inlineStr"/>
-      <c r="W23" s="7" t="inlineStr"/>
-      <c r="X23" s="7" t="inlineStr"/>
-      <c r="Y23" s="7" t="inlineStr"/>
-      <c r="Z23" s="7" t="inlineStr"/>
-      <c r="AA23" s="7" t="inlineStr"/>
+          <t>事象ステータス が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr"/>
+      <c r="N23" s="9" t="inlineStr"/>
+      <c r="O23" s="9" t="inlineStr"/>
+      <c r="P23" s="9" t="inlineStr"/>
+      <c r="Q23" s="9" t="inlineStr"/>
+      <c r="R23" s="9" t="inlineStr"/>
+      <c r="S23" s="9" t="inlineStr"/>
+      <c r="T23" s="9" t="inlineStr"/>
+      <c r="U23" s="9" t="inlineStr"/>
+      <c r="V23" s="9" t="inlineStr"/>
+      <c r="W23" s="9" t="inlineStr"/>
+      <c r="X23" s="9" t="inlineStr"/>
+      <c r="Y23" s="9" t="inlineStr"/>
+      <c r="Z23" s="9" t="inlineStr"/>
+      <c r="AA23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>E-008</t>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>E-007</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>債務者および保証人の現況 が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr"/>
-      <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr"/>
-      <c r="P24" s="7" t="inlineStr"/>
-      <c r="Q24" s="7" t="inlineStr"/>
-      <c r="R24" s="7" t="inlineStr"/>
-      <c r="S24" s="7" t="inlineStr"/>
-      <c r="T24" s="7" t="inlineStr"/>
-      <c r="U24" s="7" t="inlineStr"/>
-      <c r="V24" s="7" t="inlineStr"/>
-      <c r="W24" s="7" t="inlineStr"/>
-      <c r="X24" s="7" t="inlineStr"/>
-      <c r="Y24" s="7" t="inlineStr"/>
-      <c r="Z24" s="7" t="inlineStr"/>
-      <c r="AA24" s="7" t="inlineStr"/>
+          <t>事故及び延滞に至った原因 が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr"/>
+      <c r="N24" s="9" t="inlineStr"/>
+      <c r="O24" s="9" t="inlineStr"/>
+      <c r="P24" s="9" t="inlineStr"/>
+      <c r="Q24" s="9" t="inlineStr"/>
+      <c r="R24" s="9" t="inlineStr"/>
+      <c r="S24" s="9" t="inlineStr"/>
+      <c r="T24" s="9" t="inlineStr"/>
+      <c r="U24" s="9" t="inlineStr"/>
+      <c r="V24" s="9" t="inlineStr"/>
+      <c r="W24" s="9" t="inlineStr"/>
+      <c r="X24" s="9" t="inlineStr"/>
+      <c r="Y24" s="9" t="inlineStr"/>
+      <c r="Z24" s="9" t="inlineStr"/>
+      <c r="AA24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>E-009</t>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>E-008</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>回収、解消の方針、スケジュール が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="7" t="inlineStr"/>
-      <c r="P25" s="7" t="inlineStr"/>
-      <c r="Q25" s="7" t="inlineStr"/>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="7" t="inlineStr"/>
-      <c r="T25" s="7" t="inlineStr"/>
-      <c r="U25" s="7" t="inlineStr"/>
-      <c r="V25" s="7" t="inlineStr"/>
-      <c r="W25" s="7" t="inlineStr"/>
-      <c r="X25" s="7" t="inlineStr"/>
-      <c r="Y25" s="7" t="inlineStr"/>
-      <c r="Z25" s="7" t="inlineStr"/>
-      <c r="AA25" s="7" t="inlineStr"/>
+          <t>債務者および保証人の現況 が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr"/>
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr"/>
+      <c r="N25" s="9" t="inlineStr"/>
+      <c r="O25" s="9" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
+      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="R25" s="9" t="inlineStr"/>
+      <c r="S25" s="9" t="inlineStr"/>
+      <c r="T25" s="9" t="inlineStr"/>
+      <c r="U25" s="9" t="inlineStr"/>
+      <c r="V25" s="9" t="inlineStr"/>
+      <c r="W25" s="9" t="inlineStr"/>
+      <c r="X25" s="9" t="inlineStr"/>
+      <c r="Y25" s="9" t="inlineStr"/>
+      <c r="Z25" s="9" t="inlineStr"/>
+      <c r="AA25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>E-010</t>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>E-009</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>備考、特記事項 が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr"/>
-      <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr"/>
-      <c r="P26" s="7" t="inlineStr"/>
-      <c r="Q26" s="7" t="inlineStr"/>
-      <c r="R26" s="7" t="inlineStr"/>
-      <c r="S26" s="7" t="inlineStr"/>
-      <c r="T26" s="7" t="inlineStr"/>
-      <c r="U26" s="7" t="inlineStr"/>
-      <c r="V26" s="7" t="inlineStr"/>
-      <c r="W26" s="7" t="inlineStr"/>
-      <c r="X26" s="7" t="inlineStr"/>
-      <c r="Y26" s="7" t="inlineStr"/>
-      <c r="Z26" s="7" t="inlineStr"/>
-      <c r="AA26" s="7" t="inlineStr"/>
+          <t>回収、解消の方針、スケジュール が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
+      <c r="O26" s="9" t="inlineStr"/>
+      <c r="P26" s="9" t="inlineStr"/>
+      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="R26" s="9" t="inlineStr"/>
+      <c r="S26" s="9" t="inlineStr"/>
+      <c r="T26" s="9" t="inlineStr"/>
+      <c r="U26" s="9" t="inlineStr"/>
+      <c r="V26" s="9" t="inlineStr"/>
+      <c r="W26" s="9" t="inlineStr"/>
+      <c r="X26" s="9" t="inlineStr"/>
+      <c r="Y26" s="9" t="inlineStr"/>
+      <c r="Z26" s="9" t="inlineStr"/>
+      <c r="AA26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>E-011</t>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>E-010</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>chkAllReport が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="7" t="inlineStr"/>
-      <c r="P27" s="7" t="inlineStr"/>
-      <c r="Q27" s="7" t="inlineStr"/>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="7" t="inlineStr"/>
-      <c r="T27" s="7" t="inlineStr"/>
-      <c r="U27" s="7" t="inlineStr"/>
-      <c r="V27" s="7" t="inlineStr"/>
-      <c r="W27" s="7" t="inlineStr"/>
-      <c r="X27" s="7" t="inlineStr"/>
-      <c r="Y27" s="7" t="inlineStr"/>
-      <c r="Z27" s="7" t="inlineStr"/>
-      <c r="AA27" s="7" t="inlineStr"/>
+          <t>備考、特記事項 が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
+      <c r="O27" s="9" t="inlineStr"/>
+      <c r="P27" s="9" t="inlineStr"/>
+      <c r="Q27" s="9" t="inlineStr"/>
+      <c r="R27" s="9" t="inlineStr"/>
+      <c r="S27" s="9" t="inlineStr"/>
+      <c r="T27" s="9" t="inlineStr"/>
+      <c r="U27" s="9" t="inlineStr"/>
+      <c r="V27" s="9" t="inlineStr"/>
+      <c r="W27" s="9" t="inlineStr"/>
+      <c r="X27" s="9" t="inlineStr"/>
+      <c r="Y27" s="9" t="inlineStr"/>
+      <c r="Z27" s="9" t="inlineStr"/>
+      <c r="AA27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>E-012</t>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>E-011</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>chkReport が入力可能であること</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr"/>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr"/>
-      <c r="O28" s="7" t="inlineStr"/>
-      <c r="P28" s="7" t="inlineStr"/>
-      <c r="Q28" s="7" t="inlineStr"/>
-      <c r="R28" s="7" t="inlineStr"/>
-      <c r="S28" s="7" t="inlineStr"/>
-      <c r="T28" s="7" t="inlineStr"/>
-      <c r="U28" s="7" t="inlineStr"/>
-      <c r="V28" s="7" t="inlineStr"/>
-      <c r="W28" s="7" t="inlineStr"/>
-      <c r="X28" s="7" t="inlineStr"/>
-      <c r="Y28" s="7" t="inlineStr"/>
-      <c r="Z28" s="7" t="inlineStr"/>
-      <c r="AA28" s="7" t="inlineStr"/>
+          <t>chkAllReport が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr"/>
+      <c r="N28" s="9" t="inlineStr"/>
+      <c r="O28" s="9" t="inlineStr"/>
+      <c r="P28" s="9" t="inlineStr"/>
+      <c r="Q28" s="9" t="inlineStr"/>
+      <c r="R28" s="9" t="inlineStr"/>
+      <c r="S28" s="9" t="inlineStr"/>
+      <c r="T28" s="9" t="inlineStr"/>
+      <c r="U28" s="9" t="inlineStr"/>
+      <c r="V28" s="9" t="inlineStr"/>
+      <c r="W28" s="9" t="inlineStr"/>
+      <c r="X28" s="9" t="inlineStr"/>
+      <c r="Y28" s="9" t="inlineStr"/>
+      <c r="Z28" s="9" t="inlineStr"/>
+      <c r="AA28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>E-013</t>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>E-012</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>顧客番号 に maxlength=12 の入力チェックがあること</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O29" s="7" t="inlineStr"/>
-      <c r="P29" s="7" t="inlineStr"/>
-      <c r="Q29" s="7" t="inlineStr"/>
-      <c r="R29" s="7" t="inlineStr"/>
-      <c r="S29" s="7" t="inlineStr"/>
-      <c r="T29" s="7" t="inlineStr"/>
-      <c r="U29" s="7" t="inlineStr"/>
-      <c r="V29" s="7" t="inlineStr"/>
-      <c r="W29" s="7" t="inlineStr"/>
-      <c r="X29" s="7" t="inlineStr"/>
-      <c r="Y29" s="7" t="inlineStr"/>
-      <c r="Z29" s="7" t="inlineStr"/>
-      <c r="AA29" s="7" t="inlineStr"/>
+          <t>chkReport が入力可能であること</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr"/>
+      <c r="K29" s="9" t="inlineStr"/>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr"/>
+      <c r="O29" s="9" t="inlineStr"/>
+      <c r="P29" s="9" t="inlineStr"/>
+      <c r="Q29" s="9" t="inlineStr"/>
+      <c r="R29" s="9" t="inlineStr"/>
+      <c r="S29" s="9" t="inlineStr"/>
+      <c r="T29" s="9" t="inlineStr"/>
+      <c r="U29" s="9" t="inlineStr"/>
+      <c r="V29" s="9" t="inlineStr"/>
+      <c r="W29" s="9" t="inlineStr"/>
+      <c r="X29" s="9" t="inlineStr"/>
+      <c r="Y29" s="9" t="inlineStr"/>
+      <c r="Z29" s="9" t="inlineStr"/>
+      <c r="AA29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>E-014</t>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>E-013</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>事故及び延滞に至った原因 に maxlength=2000 の入力チェックがあること</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr"/>
-      <c r="Q30" s="7" t="inlineStr"/>
-      <c r="R30" s="7" t="inlineStr"/>
-      <c r="S30" s="7" t="inlineStr"/>
-      <c r="T30" s="7" t="inlineStr"/>
-      <c r="U30" s="7" t="inlineStr"/>
-      <c r="V30" s="7" t="inlineStr"/>
-      <c r="W30" s="7" t="inlineStr"/>
-      <c r="X30" s="7" t="inlineStr"/>
-      <c r="Y30" s="7" t="inlineStr"/>
-      <c r="Z30" s="7" t="inlineStr"/>
-      <c r="AA30" s="7" t="inlineStr"/>
+          <t>顧客番号 に maxlength=12 の入力チェックがあること</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr"/>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr"/>
+      <c r="P30" s="9" t="inlineStr"/>
+      <c r="Q30" s="9" t="inlineStr"/>
+      <c r="R30" s="9" t="inlineStr"/>
+      <c r="S30" s="9" t="inlineStr"/>
+      <c r="T30" s="9" t="inlineStr"/>
+      <c r="U30" s="9" t="inlineStr"/>
+      <c r="V30" s="9" t="inlineStr"/>
+      <c r="W30" s="9" t="inlineStr"/>
+      <c r="X30" s="9" t="inlineStr"/>
+      <c r="Y30" s="9" t="inlineStr"/>
+      <c r="Z30" s="9" t="inlineStr"/>
+      <c r="AA30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>E-015</t>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>E-014</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>債務者および保証人の現況 に maxlength=2000 の入力チェックがあること</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="7" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr"/>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" s="7" t="inlineStr"/>
-      <c r="T31" s="7" t="inlineStr"/>
-      <c r="U31" s="7" t="inlineStr"/>
-      <c r="V31" s="7" t="inlineStr"/>
-      <c r="W31" s="7" t="inlineStr"/>
-      <c r="X31" s="7" t="inlineStr"/>
-      <c r="Y31" s="7" t="inlineStr"/>
-      <c r="Z31" s="7" t="inlineStr"/>
-      <c r="AA31" s="7" t="inlineStr"/>
+          <t>事故及び延滞に至った原因 に maxlength=2000 の入力チェックがあること</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr"/>
+      <c r="N31" s="9" t="inlineStr"/>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr"/>
+      <c r="Q31" s="9" t="inlineStr"/>
+      <c r="R31" s="9" t="inlineStr"/>
+      <c r="S31" s="9" t="inlineStr"/>
+      <c r="T31" s="9" t="inlineStr"/>
+      <c r="U31" s="9" t="inlineStr"/>
+      <c r="V31" s="9" t="inlineStr"/>
+      <c r="W31" s="9" t="inlineStr"/>
+      <c r="X31" s="9" t="inlineStr"/>
+      <c r="Y31" s="9" t="inlineStr"/>
+      <c r="Z31" s="9" t="inlineStr"/>
+      <c r="AA31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>E-016</t>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>E-015</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>回収、解消の方針、スケジュール に maxlength=2000 の入力チェックがあること</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" s="7" t="inlineStr"/>
-      <c r="P32" s="7" t="inlineStr"/>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr"/>
-      <c r="S32" s="7" t="inlineStr"/>
-      <c r="T32" s="7" t="inlineStr"/>
-      <c r="U32" s="7" t="inlineStr"/>
-      <c r="V32" s="7" t="inlineStr"/>
-      <c r="W32" s="7" t="inlineStr"/>
-      <c r="X32" s="7" t="inlineStr"/>
-      <c r="Y32" s="7" t="inlineStr"/>
-      <c r="Z32" s="7" t="inlineStr"/>
-      <c r="AA32" s="7" t="inlineStr"/>
+          <t>債務者および保証人の現況 に maxlength=2000 の入力チェックがあること</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
+      <c r="N32" s="9" t="inlineStr"/>
+      <c r="O32" s="9" t="inlineStr"/>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="inlineStr"/>
+      <c r="R32" s="9" t="inlineStr"/>
+      <c r="S32" s="9" t="inlineStr"/>
+      <c r="T32" s="9" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" s="9" t="inlineStr"/>
+      <c r="W32" s="9" t="inlineStr"/>
+      <c r="X32" s="9" t="inlineStr"/>
+      <c r="Y32" s="9" t="inlineStr"/>
+      <c r="Z32" s="9" t="inlineStr"/>
+      <c r="AA32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>E-017</t>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>E-016</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>備考、特記事項 に maxlength=2000 の入力チェックがあること</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" s="7" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr"/>
-      <c r="Q33" s="7" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr"/>
-      <c r="T33" s="7" t="inlineStr"/>
-      <c r="U33" s="7" t="inlineStr"/>
-      <c r="V33" s="7" t="inlineStr"/>
-      <c r="W33" s="7" t="inlineStr"/>
-      <c r="X33" s="7" t="inlineStr"/>
-      <c r="Y33" s="7" t="inlineStr"/>
-      <c r="Z33" s="7" t="inlineStr"/>
-      <c r="AA33" s="7" t="inlineStr"/>
+          <t>回収、解消の方針、スケジュール に maxlength=2000 の入力チェックがあること</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr"/>
+      <c r="N33" s="9" t="inlineStr"/>
+      <c r="O33" s="9" t="inlineStr"/>
+      <c r="P33" s="9" t="inlineStr"/>
+      <c r="Q33" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R33" s="9" t="inlineStr"/>
+      <c r="S33" s="9" t="inlineStr"/>
+      <c r="T33" s="9" t="inlineStr"/>
+      <c r="U33" s="9" t="inlineStr"/>
+      <c r="V33" s="9" t="inlineStr"/>
+      <c r="W33" s="9" t="inlineStr"/>
+      <c r="X33" s="9" t="inlineStr"/>
+      <c r="Y33" s="9" t="inlineStr"/>
+      <c r="Z33" s="9" t="inlineStr"/>
+      <c r="AA33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>E-018</t>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>E-017</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>イベント実行後の画面表示・処理結果が正しいこと</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-      <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" s="7" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr"/>
-      <c r="Q34" s="7" t="inlineStr"/>
-      <c r="R34" s="7" t="inlineStr"/>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W34" s="7" t="inlineStr"/>
-      <c r="X34" s="7" t="inlineStr"/>
-      <c r="Y34" s="7" t="inlineStr"/>
-      <c r="Z34" s="7" t="inlineStr"/>
-      <c r="AA34" s="7" t="inlineStr"/>
+          <t>備考、特記事項 に maxlength=2000 の入力チェックがあること</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr"/>
+      <c r="N34" s="9" t="inlineStr"/>
+      <c r="O34" s="9" t="inlineStr"/>
+      <c r="P34" s="9" t="inlineStr"/>
+      <c r="Q34" s="9" t="inlineStr"/>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr"/>
+      <c r="T34" s="9" t="inlineStr"/>
+      <c r="U34" s="9" t="inlineStr"/>
+      <c r="V34" s="9" t="inlineStr"/>
+      <c r="W34" s="9" t="inlineStr"/>
+      <c r="X34" s="9" t="inlineStr"/>
+      <c r="Y34" s="9" t="inlineStr"/>
+      <c r="Z34" s="9" t="inlineStr"/>
+      <c r="AA34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>E-019</t>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>E-018</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>一覧データが正しく表示されること</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" s="7" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr"/>
-      <c r="Q35" s="7" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" s="7" t="inlineStr"/>
-      <c r="T35" s="7" t="inlineStr"/>
-      <c r="U35" s="7" t="inlineStr"/>
-      <c r="V35" s="7" t="inlineStr"/>
-      <c r="W35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Y35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Z35" s="7" t="inlineStr"/>
-      <c r="AA35" s="7" t="inlineStr"/>
+          <t>イベント実行後の画面表示・処理結果が正しいこと</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr"/>
+      <c r="K35" s="9" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr"/>
+      <c r="N35" s="9" t="inlineStr"/>
+      <c r="O35" s="9" t="inlineStr"/>
+      <c r="P35" s="9" t="inlineStr"/>
+      <c r="Q35" s="9" t="inlineStr"/>
+      <c r="R35" s="9" t="inlineStr"/>
+      <c r="S35" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T35" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U35" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V35" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr"/>
+      <c r="X35" s="9" t="inlineStr"/>
+      <c r="Y35" s="9" t="inlineStr"/>
+      <c r="Z35" s="9" t="inlineStr"/>
+      <c r="AA35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>E-020</t>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>E-019</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>参照モード時に対象コントロールが非活性となること</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
-      <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-      <c r="O36" s="7" t="inlineStr"/>
-      <c r="P36" s="7" t="inlineStr"/>
-      <c r="Q36" s="7" t="inlineStr"/>
-      <c r="R36" s="7" t="inlineStr"/>
-      <c r="S36" s="7" t="inlineStr"/>
-      <c r="T36" s="7" t="inlineStr"/>
-      <c r="U36" s="7" t="inlineStr"/>
-      <c r="V36" s="7" t="inlineStr"/>
-      <c r="W36" s="7" t="inlineStr"/>
-      <c r="X36" s="7" t="inlineStr"/>
-      <c r="Y36" s="7" t="inlineStr"/>
-      <c r="Z36" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA36" s="7" t="inlineStr"/>
+          <t>一覧データが正しく表示されること</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr"/>
+      <c r="N36" s="9" t="inlineStr"/>
+      <c r="O36" s="9" t="inlineStr"/>
+      <c r="P36" s="9" t="inlineStr"/>
+      <c r="Q36" s="9" t="inlineStr"/>
+      <c r="R36" s="9" t="inlineStr"/>
+      <c r="S36" s="9" t="inlineStr"/>
+      <c r="T36" s="9" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" s="9" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X36" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y36" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z36" s="9" t="inlineStr"/>
+      <c r="AA36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>E-021</t>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>E-020</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>対象コントロール数: 15</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" s="7" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr"/>
-      <c r="Q37" s="7" t="inlineStr"/>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" s="7" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr"/>
-      <c r="U37" s="7" t="inlineStr"/>
-      <c r="V37" s="7" t="inlineStr"/>
-      <c r="W37" s="7" t="inlineStr"/>
-      <c r="X37" s="7" t="inlineStr"/>
-      <c r="Y37" s="7" t="inlineStr"/>
-      <c r="Z37" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA37" s="7" t="inlineStr"/>
+          <t>参照モード時に対象コントロールが非活性となること</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr"/>
+      <c r="N37" s="9" t="inlineStr"/>
+      <c r="O37" s="9" t="inlineStr"/>
+      <c r="P37" s="9" t="inlineStr"/>
+      <c r="Q37" s="9" t="inlineStr"/>
+      <c r="R37" s="9" t="inlineStr"/>
+      <c r="S37" s="9" t="inlineStr"/>
+      <c r="T37" s="9" t="inlineStr"/>
+      <c r="U37" s="9" t="inlineStr"/>
+      <c r="V37" s="9" t="inlineStr"/>
+      <c r="W37" s="9" t="inlineStr"/>
+      <c r="X37" s="9" t="inlineStr"/>
+      <c r="Y37" s="9" t="inlineStr"/>
+      <c r="Z37" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>E-022</t>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>E-021</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>更新時に排他制御が実施されること</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-      <c r="O38" s="7" t="inlineStr"/>
-      <c r="P38" s="7" t="inlineStr"/>
-      <c r="Q38" s="7" t="inlineStr"/>
-      <c r="R38" s="7" t="inlineStr"/>
-      <c r="S38" s="7" t="inlineStr"/>
-      <c r="T38" s="7" t="inlineStr"/>
-      <c r="U38" s="7" t="inlineStr"/>
-      <c r="V38" s="7" t="inlineStr"/>
-      <c r="W38" s="7" t="inlineStr"/>
-      <c r="X38" s="7" t="inlineStr"/>
-      <c r="Y38" s="7" t="inlineStr"/>
-      <c r="Z38" s="7" t="inlineStr"/>
-      <c r="AA38" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>対象コントロール数: 15</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr"/>
+      <c r="K38" s="9" t="inlineStr"/>
+      <c r="L38" s="9" t="inlineStr"/>
+      <c r="M38" s="9" t="inlineStr"/>
+      <c r="N38" s="9" t="inlineStr"/>
+      <c r="O38" s="9" t="inlineStr"/>
+      <c r="P38" s="9" t="inlineStr"/>
+      <c r="Q38" s="9" t="inlineStr"/>
+      <c r="R38" s="9" t="inlineStr"/>
+      <c r="S38" s="9" t="inlineStr"/>
+      <c r="T38" s="9" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" s="9" t="inlineStr"/>
+      <c r="W38" s="9" t="inlineStr"/>
+      <c r="X38" s="9" t="inlineStr"/>
+      <c r="Y38" s="9" t="inlineStr"/>
+      <c r="Z38" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="n"/>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
-      <c r="AA39" s="2" t="n"/>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>E-022</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>更新時に排他制御が実施されること</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr"/>
+      <c r="K39" s="9" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr"/>
+      <c r="N39" s="9" t="inlineStr"/>
+      <c r="O39" s="9" t="inlineStr"/>
+      <c r="P39" s="9" t="inlineStr"/>
+      <c r="Q39" s="9" t="inlineStr"/>
+      <c r="R39" s="9" t="inlineStr"/>
+      <c r="S39" s="9" t="inlineStr"/>
+      <c r="T39" s="9" t="inlineStr"/>
+      <c r="U39" s="9" t="inlineStr"/>
+      <c r="V39" s="9" t="inlineStr"/>
+      <c r="W39" s="9" t="inlineStr"/>
+      <c r="X39" s="9" t="inlineStr"/>
+      <c r="Y39" s="9" t="inlineStr"/>
+      <c r="Z39" s="9" t="inlineStr"/>
+      <c r="AA39" s="9" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="n"/>
+      <c r="Z40" s="2" t="n"/>
+      <c r="AA40" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A17:A39"/>
-    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A18:A40"/>
+    <mergeCell ref="A7:A11"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
